--- a/database/Database_Simulasi_TKA_SDN_Johar_Baru_01_Pagi.xlsx
+++ b/database/Database_Simulasi_TKA_SDN_Johar_Baru_01_Pagi.xlsx
@@ -6,6 +6,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA_SISWA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANK_SOAL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HASIL_UJIAN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UJIAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SESI_UJIAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENGGUNA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENGATURAN" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOG_AKTIVITAS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -29,13 +34,21 @@
       <color theme="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -44,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -62,6 +75,7 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,10 +351,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="4" max="4"/>
     <col width="16.13" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -377,6 +398,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PASSWORD_SALT</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>LOGIN_TERAKHIR</t>
         </is>
       </c>
     </row>
@@ -426,19 +452,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J999"/>
+  <dimension ref="A1:O999"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="8" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
     <col width="16" customWidth="1" style="5" min="2" max="2"/>
-    <col width="6.38" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
     <col width="36.5" customWidth="1" style="5" min="4" max="4"/>
-    <col width="10.25" customWidth="1" style="5" min="5" max="5"/>
-    <col width="8.75" customWidth="1" style="5" min="6" max="6"/>
-    <col width="13.75" customWidth="1" style="5" min="7" max="7"/>
-    <col width="7.13" customWidth="1" style="5" min="8" max="8"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
     <col width="15" customWidth="1" style="5" min="9" max="9"/>
-    <col width="5.75" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="11" max="11"/>
+    <col width="16" customWidth="1" style="5" min="12" max="12"/>
+    <col width="16" customWidth="1" style="5" min="13" max="13"/>
+    <col width="16" customWidth="1" style="5" min="14" max="14"/>
+    <col width="16" customWidth="1" style="5" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +521,31 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SKOR</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>TIPE_SOAL</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>GAMBAR_ID</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>PEMBAHASAN</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>DIBUAT</t>
         </is>
       </c>
     </row>
@@ -8608,19 +8664,26 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="8.380000000000001" customWidth="1" style="5" min="1" max="1"/>
-    <col width="8.880000000000001" customWidth="1" style="5" min="2" max="2"/>
-    <col width="12" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
     <col width="14.63" customWidth="1" style="5" min="4" max="4"/>
-    <col width="5.13" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
     <col width="14.38" customWidth="1" style="5" min="6" max="6"/>
     <col width="14" customWidth="1" style="5" min="7" max="7"/>
-    <col width="13.13" customWidth="1" style="5" min="8" max="9"/>
-    <col width="13" customWidth="1" style="5" min="9" max="9"/>
-    <col width="13" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="8" max="9"/>
+    <col width="16" customWidth="1" style="5" min="9" max="9"/>
+    <col width="16" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="11" max="11"/>
+    <col width="16" customWidth="1" style="5" min="12" max="12"/>
+    <col width="16" customWidth="1" style="5" min="13" max="13"/>
+    <col width="16" customWidth="1" style="5" min="14" max="14"/>
+    <col width="16" customWidth="1" style="5" min="15" max="15"/>
+    <col width="16" customWidth="1" style="5" min="16" max="16"/>
+    <col width="16" customWidth="1" style="5" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8674,6 +8737,443 @@
           <t>MATA_PELAJARAN</t>
         </is>
       </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>KELAS</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>ID_UJIAN</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>NAMA_UJIAN</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>JUMLAH_KOSONG</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>JAWABAN</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>ID_SESI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
+    <col width="16" customWidth="1" style="5" min="9" max="9"/>
+    <col width="16" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="11" max="11"/>
+    <col width="16" customWidth="1" style="5" min="12" max="12"/>
+    <col width="16" customWidth="1" style="5" min="13" max="13"/>
+    <col width="16" customWidth="1" style="5" min="14" max="14"/>
+    <col width="16" customWidth="1" style="5" min="15" max="15"/>
+    <col width="16" customWidth="1" style="5" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ID_UJIAN</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>NAMA_UJIAN</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>MATA_PELAJARAN</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>KELAS</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>DURASI_MENIT</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>JUMLAH_SOAL</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>WAKTU_MULAI</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>WAKTU_SELESAI</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>TOKEN</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>ACAK_SOAL</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>ACAK_OPSI</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>TAMPILKAN_NILAI</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>TAMPILKAN_PEMBAHASAN</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>MAKS_PERCOBAAN</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>DIBUAT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
+    <col width="16" customWidth="1" style="5" min="9" max="9"/>
+    <col width="16" customWidth="1" style="5" min="10" max="10"/>
+    <col width="16" customWidth="1" style="5" min="11" max="11"/>
+    <col width="16" customWidth="1" style="5" min="12" max="12"/>
+    <col width="16" customWidth="1" style="5" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ID_SESI</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>ID_UJIAN</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>NISN</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>NAMA_SISWA</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>KELAS</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>WAKTU_MULAI</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>BATAS_WAKTU</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>URUTAN</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>JAWABAN</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>RAGU</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>TERAKHIR_AKTIF</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
+    <col width="16" customWidth="1" style="5" min="6" max="6"/>
+    <col width="16" customWidth="1" style="5" min="7" max="7"/>
+    <col width="16" customWidth="1" style="5" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ID_PENGGUNA</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>NAMA</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>PASSWORD_HASH</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>PASSWORD_SALT</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>PERAN</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>LOGIN_TERAKHIR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>KUNCI</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>NILAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>NAMA_SEKOLAH</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>SDN Johar Baru 01 Pagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>TAHUN_AJARAN</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>KKM</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>SISWA_BOLEH_GANTI_PASSWORD</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16" customWidth="1" style="5" min="3" max="3"/>
+    <col width="16" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>WAKTU</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>PENGGUNA</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>PERAN</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>AKSI</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>DETAIL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
